--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_256_R26.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_256_R26.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W. GABRIEL</t>
+          <t>A. OBST</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1435</v>
+        <v>6.3757</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5353</v>
+        <v>3.4346</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6082</v>
+        <v>2.9411</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3229</v>
+        <v>1.7471</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5064</v>
+        <v>-1.0901</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8165</v>
+        <v>2.8372</v>
       </c>
       <c r="J2" t="n">
-        <v>3.002</v>
+        <v>2.3262</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6034</v>
+        <v>-0.6246</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3986</v>
+        <v>2.9508</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6791</v>
+        <v>-0.579</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.097</v>
+        <v>-0.4655</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5821</v>
+        <v>-0.1136</v>
       </c>
       <c r="P2" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q2" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5515</v>
+        <v>3.2473</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1221</v>
+        <v>1.0203</v>
       </c>
       <c r="T2" t="n">
-        <v>2.497</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6251</v>
+        <v>0.2728</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4665</v>
+        <v>2.6805</v>
       </c>
       <c r="W2" t="n">
-        <v>1.3558</v>
+        <v>2.6805</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. OBST</t>
+          <t>W. GABRIEL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3301</v>
+        <v>5.8034</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5907</v>
+        <v>3.4304</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7395</v>
+        <v>2.373</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7471</v>
+        <v>2.3229</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0901</v>
+        <v>1.5064</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8372</v>
+        <v>0.8165</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3262</v>
+        <v>3.002</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.6246</v>
+        <v>1.6034</v>
       </c>
       <c r="L3" t="n">
-        <v>2.9508</v>
+        <v>1.3986</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.579</v>
+        <v>-0.6791</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4655</v>
+        <v>-0.097</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1136</v>
+        <v>-0.5821</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q3" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R3" t="n">
-        <v>3.2473</v>
+        <v>2.5515</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0253</v>
+        <v>1.782</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0965</v>
+        <v>1.3921</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0712</v>
+        <v>0.3899</v>
       </c>
       <c r="V3" t="n">
-        <v>2.6805</v>
+        <v>1.4665</v>
       </c>
       <c r="W3" t="n">
-        <v>2.6805</v>
+        <v>1.3558</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.1107</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0829</v>
+        <v>2.3587</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.6874</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1805</v>
+        <v>3.0461</v>
       </c>
       <c r="G4" t="n">
         <v>1.7137</v>
@@ -766,13 +766,13 @@
         <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4594</v>
+        <v>0.7352</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6844</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7749</v>
+        <v>0.6405</v>
       </c>
       <c r="V4" t="n">
         <v>0.1418</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7117</v>
+        <v>1.9476</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.634</v>
+        <v>-0.3981</v>
       </c>
       <c r="F5" t="n">
         <v>2.3456</v>
@@ -844,10 +844,10 @@
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3892</v>
+        <v>0.6251</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3541</v>
+        <v>0.59</v>
       </c>
       <c r="U5" t="n">
         <v>0.0351</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. DA SILVA</t>
+          <t>J. JESSUP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4859</v>
+        <v>0.249</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5833</v>
+        <v>-0.4631</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0693</v>
+        <v>0.7121</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.7892</v>
+        <v>-0.5344</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0444</v>
+        <v>3.4609</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8336</v>
+        <v>-3.9953</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8706</v>
+        <v>-0.2736</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5917</v>
+        <v>3.2434</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4623</v>
+        <v>-3.5169</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9186</v>
+        <v>-0.2608</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5473</v>
+        <v>0.2175</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3713</v>
+        <v>-0.4783</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6237</v>
+        <v>2.7834</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8112</v>
+        <v>0.232</v>
       </c>
       <c r="T6" t="n">
-        <v>1.447</v>
+        <v>-0.1019</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3642</v>
+        <v>0.3339</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X. RATHAN-MAYES</t>
+          <t>O. DA SILVA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2917</v>
+        <v>-0.0524</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1494</v>
+        <v>-0.8192</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4411</v>
+        <v>0.7668</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6291</v>
+        <v>-1.7892</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6291</v>
+        <v>0.0444</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-1.8336</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7863</v>
+        <v>-0.8706</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7863</v>
+        <v>0.5917</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.4623</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1573</v>
+        <v>-0.9186</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1573</v>
+        <v>-0.5473</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.3713</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9208</v>
+        <v>1.2729</v>
       </c>
       <c r="T7" t="n">
-        <v>0.637</v>
+        <v>1.2111</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2838</v>
+        <v>0.0617</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. JESSUP</t>
+          <t>X. RATHAN-MAYES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.229</v>
+        <v>-0.1966</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5377</v>
+        <v>-0.5032</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3088</v>
+        <v>0.3066</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5344</v>
+        <v>-0.6291</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4609</v>
+        <v>-0.6291</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.9953</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2736</v>
+        <v>-0.7863</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2434</v>
+        <v>-0.7863</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.5169</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2608</v>
+        <v>0.1573</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2175</v>
+        <v>0.1573</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4783</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6237</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7834</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.246</v>
+        <v>0.4325</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1766</v>
+        <v>0.2831</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0694</v>
+        <v>0.1494</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.618</v>
+        <v>-0.8471</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4011</v>
+        <v>0.004</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0191</v>
+        <v>-0.8511</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1251</v>
@@ -1156,13 +1156,13 @@
         <v>1.8556</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4686</v>
+        <v>1.2395</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7774</v>
+        <v>1.3803</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3088</v>
+        <v>-0.1408</v>
       </c>
       <c r="V9" t="n">
         <v>-1.4975</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8007</v>
+        <v>-1.6149</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7273</v>
+        <v>-3.3735</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9267</v>
+        <v>1.7586</v>
       </c>
       <c r="G10" t="n">
         <v>0.415</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4775</v>
+        <v>0.6633</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3734</v>
+        <v>-0.0196</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8509</v>
+        <v>0.6829</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0404</v>
+        <v>-2.5801</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.367</v>
+        <v>-4.0747</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3266</v>
+        <v>1.4946</v>
       </c>
       <c r="G11" t="n">
         <v>0.06619999999999999</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>0.749</v>
+        <v>0.2093</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9752</v>
+        <v>0.2675</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2262</v>
+        <v>-0.0582</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5361</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.724</v>
+        <v>-5.4362</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.8424</v>
+        <v>-6.5882</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1184</v>
+        <v>1.152</v>
       </c>
       <c r="G12" t="n">
         <v>-5.0477</v>
@@ -1390,13 +1390,13 @@
         <v>2.0876</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3025</v>
+        <v>-0.0147</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4936</v>
+        <v>-0.2394</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1911</v>
+        <v>0.2247</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1418</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.633699999999999</v>
+        <v>6.007099999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.4116</v>
+        <v>-10.0384</v>
       </c>
       <c r="F13" t="n">
-        <v>16.0456</v>
+        <v>16.0454</v>
       </c>
       <c r="G13" t="n">
         <v>-1.9298</v>
@@ -1453,7 +1453,7 @@
         <v>-1.9113</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7639999999999999</v>
+        <v>0.764</v>
       </c>
       <c r="O13" t="n">
         <v>-2.6755</v>
@@ -1468,10 +1468,10 @@
         <v>19.716</v>
       </c>
       <c r="S13" t="n">
-        <v>7.824</v>
+        <v>8.1974</v>
       </c>
       <c r="T13" t="n">
-        <v>5.232</v>
+        <v>5.6054</v>
       </c>
       <c r="U13" t="n">
         <v>2.5919</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3732</v>
+        <v>3.5977</v>
       </c>
       <c r="E14" t="n">
         <v>4.221</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8477</v>
+        <v>-0.6232</v>
       </c>
       <c r="G14" t="n">
         <v>-0.7027</v>
@@ -1546,13 +1546,13 @@
         <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4938</v>
+        <v>-0.2693</v>
       </c>
       <c r="T14" t="n">
         <v>-0.1019</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3918</v>
+        <v>-0.1674</v>
       </c>
       <c r="V14" t="n">
         <v>3.6419</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5265</v>
+        <v>2.0262</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4267</v>
+        <v>-0.3087</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9531</v>
+        <v>2.3349</v>
       </c>
       <c r="G15" t="n">
         <v>1.4228</v>
@@ -1624,13 +1624,13 @@
         <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-0.3244</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5254</v>
+        <v>-0.1436</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7876</v>
+        <v>0.4002</v>
       </c>
       <c r="E16" t="n">
-        <v>0.849</v>
+        <v>0.4952</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0614</v>
+        <v>-0.095</v>
       </c>
       <c r="G16" t="n">
         <v>0.0934</v>
@@ -1702,13 +1702,13 @@
         <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3211</v>
+        <v>-0.7086</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1019</v>
+        <v>-0.4558</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2192</v>
+        <v>-0.2528</v>
       </c>
       <c r="V16" t="n">
         <v>-1.0722</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0429</v>
+        <v>0.3194</v>
       </c>
       <c r="E17" t="n">
-        <v>0.55</v>
+        <v>1.1398</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5071</v>
+        <v>-0.8204</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7454</v>
@@ -1780,13 +1780,13 @@
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4437</v>
+        <v>-0.1672</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8962</v>
+        <v>-0.3064</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4525</v>
+        <v>0.1393</v>
       </c>
       <c r="V17" t="n">
         <v>0.5361</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. RHODEN</t>
+          <t>Y. OUATTARA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4991</v>
+        <v>0.0279</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.2505</v>
+        <v>-2.0775</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7514</v>
+        <v>2.1054</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8397</v>
+        <v>0.4457</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7226</v>
+        <v>-0.6218</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1171</v>
+        <v>1.0675</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1142</v>
+        <v>-0.6623</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8304</v>
+        <v>-0.7359</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7163</v>
+        <v>0.0736</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7255</v>
+        <v>1.108</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1078</v>
+        <v>0.1141</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8333</v>
+        <v>0.9939</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.5515</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>3.0154</v>
+        <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4084</v>
+        <v>-0.6497000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.955</v>
+        <v>-0.2555</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4533</v>
+        <v>-0.3943</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Y. OUATTARA</t>
+          <t>J. RHODEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6398</v>
+        <v>-0.0324</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1955</v>
+        <v>-2.8967</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5557</v>
+        <v>2.8643</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4457</v>
+        <v>0.8397</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6218</v>
+        <v>0.7226</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0675</v>
+        <v>0.1171</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6623</v>
+        <v>0.1142</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7359</v>
+        <v>0.8304</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0736</v>
+        <v>-0.7163</v>
       </c>
       <c r="M19" t="n">
-        <v>1.108</v>
+        <v>0.7255</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1141</v>
+        <v>-0.1078</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9939</v>
+        <v>0.8333</v>
       </c>
       <c r="P19" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-2.5515</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3917</v>
+        <v>3.0154</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3175</v>
+        <v>-0.9416</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3734</v>
+        <v>-0.6012</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9441000000000001</v>
+        <v>-0.3404</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>S. HERRERA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7312</v>
+        <v>-0.5131</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8337</v>
+        <v>-1.6559</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1024</v>
+        <v>1.1427</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2793</v>
+        <v>0.5518</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5774</v>
+        <v>0.5619</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8567</v>
+        <v>-0.01</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6287</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7023</v>
+        <v>1.1091</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0736</v>
+        <v>-0.3213</v>
       </c>
       <c r="M20" t="n">
-        <v>0.908</v>
+        <v>-0.236</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1249</v>
+        <v>-0.5473</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7831</v>
+        <v>0.3113</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3195</v>
+        <v>-2.5515</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3195</v>
+        <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>0.456</v>
+        <v>-0.6732</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0272</v>
+        <v>-0.4283</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4832</v>
+        <v>-0.2449</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.4665</v>
+        <v>0.5361</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1418</v>
+        <v>0.5361</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. HERRERA</t>
+          <t>J. ROBINSON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8498</v>
+        <v>-0.5574</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8918</v>
+        <v>-4.1313</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0419</v>
+        <v>3.5739</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5518</v>
+        <v>0.9503</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5619</v>
+        <v>-0.7359</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.01</v>
+        <v>1.6862</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7877999999999999</v>
+        <v>-0.2474</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1091</v>
+        <v>-1.4684</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3213</v>
+        <v>1.221</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.236</v>
+        <v>1.1977</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5473</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3113</v>
+        <v>0.4653</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.5515</v>
+        <v>-3.4793</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6237</v>
+        <v>3.2473</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.01</v>
+        <v>-1.2757</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6642</v>
+        <v>-0.4046</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3457</v>
+        <v>-0.8711</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. ROBINSON</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1065</v>
+        <v>-1.3032</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8954</v>
+        <v>-3.0696</v>
       </c>
       <c r="F22" t="n">
-        <v>2.7889</v>
+        <v>1.7664</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9503</v>
+        <v>0.2793</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7359</v>
+        <v>-0.5774</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6862</v>
+        <v>0.8567</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2474</v>
+        <v>-0.6287</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.4684</v>
+        <v>-0.7023</v>
       </c>
       <c r="L22" t="n">
-        <v>1.221</v>
+        <v>0.0736</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1977</v>
+        <v>0.908</v>
       </c>
       <c r="N22" t="n">
-        <v>0.7324000000000001</v>
+        <v>0.1249</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4653</v>
+        <v>0.7831</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R22" t="n">
-        <v>3.2473</v>
+        <v>2.3195</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.8249</v>
+        <v>-0.116</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1687</v>
+        <v>-0.2631</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.6562</v>
+        <v>0.1472</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.4665</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>J. MORGAN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,40 +2203,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3416</v>
+        <v>-1.8792</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8314</v>
+        <v>-1.3139</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4897</v>
+        <v>-0.5653</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6127</v>
+        <v>0.769</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6865</v>
+        <v>0.6652</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0737</v>
+        <v>0.1038</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5518999999999999</v>
+        <v>1.1547</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7359</v>
+        <v>0.1008</v>
       </c>
       <c r="L23" t="n">
-        <v>0.184</v>
+        <v>1.0539</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0608</v>
+        <v>-0.3858</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0495</v>
+        <v>0.5644</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1103</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P23" t="n">
         <v>-0.9278</v>
@@ -2248,28 +2248,28 @@
         <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9875</v>
+        <v>-0.3646</v>
       </c>
       <c r="T23" t="n">
-        <v>1.6869</v>
+        <v>-0.1491</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6994</v>
+        <v>-0.2155</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.7886</v>
+        <v>-1.3558</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6468</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1418</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. MORGAN</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,40 +2281,40 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7943</v>
+        <v>-2.1838</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9037</v>
+        <v>-3.0109</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8905999999999999</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>0.769</v>
+        <v>-0.6127</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6652</v>
+        <v>-0.6865</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1038</v>
+        <v>0.0737</v>
       </c>
       <c r="J24" t="n">
-        <v>1.1547</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1008</v>
+        <v>-0.7359</v>
       </c>
       <c r="L24" t="n">
-        <v>1.0539</v>
+        <v>0.184</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3858</v>
+        <v>-0.0608</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5644</v>
+        <v>0.0495</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-0.1103</v>
       </c>
       <c r="P24" t="n">
         <v>-0.9278</v>
@@ -2326,22 +2326,22 @@
         <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2797</v>
+        <v>0.1454</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7389</v>
+        <v>0.5074</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.362</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.3558</v>
+        <v>-0.7886</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.6468</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.3558</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.4016</v>
+        <v>-3.1772</v>
       </c>
       <c r="E25" t="n">
         <v>-2.9008</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5008</v>
+        <v>-0.2763</v>
       </c>
       <c r="G25" t="n">
         <v>-1.3614</v>
@@ -2404,13 +2404,13 @@
         <v>1.1598</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3444</v>
+        <v>-0.1199</v>
       </c>
       <c r="T25" t="n">
         <v>0.0474</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3918</v>
+        <v>-0.1674</v>
       </c>
       <c r="V25" t="n">
         <v>-0.5361</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.6337</v>
+        <v>-3.274900000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-15.5095</v>
+        <v>-15.5093</v>
       </c>
       <c r="F26" t="n">
-        <v>9.875500000000001</v>
+        <v>12.2345</v>
       </c>
       <c r="G26" t="n">
         <v>1.929800000000001</v>
@@ -2458,22 +2458,22 @@
         <v>1.9115</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.7641999999999999</v>
+        <v>-0.7642</v>
       </c>
       <c r="L26" t="n">
         <v>2.6756</v>
       </c>
       <c r="M26" t="n">
-        <v>0.01830000000000009</v>
+        <v>0.01830000000000032</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.9703999999999997</v>
+        <v>-0.9704</v>
       </c>
       <c r="O26" t="n">
         <v>0.9886999999999998</v>
       </c>
       <c r="P26" t="n">
-        <v>1.159799999999999</v>
+        <v>1.1598</v>
       </c>
       <c r="Q26" t="n">
         <v>-19.7161</v>
@@ -2482,13 +2482,13 @@
         <v>20.8758</v>
       </c>
       <c r="S26" t="n">
-        <v>-7.8241</v>
+        <v>-5.4648</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.5918</v>
+        <v>-2.5919</v>
       </c>
       <c r="U26" t="n">
-        <v>-5.231999999999999</v>
+        <v>-2.8729</v>
       </c>
       <c r="V26" t="n">
         <v>-0.8993999999999995</v>
